--- a/artfynd/A 15530-2024 artfynd.xlsx
+++ b/artfynd/A 15530-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>113798453</v>
       </c>
       <c r="B4" t="n">
-        <v>78246</v>
+        <v>78262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">

--- a/artfynd/A 15530-2024 artfynd.xlsx
+++ b/artfynd/A 15530-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>113798453</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15530-2024 artfynd.xlsx
+++ b/artfynd/A 15530-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY87"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10336,7 +10336,7 @@
         <v>121329913</v>
       </c>
       <c r="B87" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10454,6 +10454,130 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>121405035</v>
+      </c>
+      <c r="B88" t="n">
+        <v>56563</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Torpaskogsberget, Hakunge, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>685919</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6605118</v>
+      </c>
+      <c r="S88" t="n">
+        <v>39</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Michael Staff</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Michael Staff</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15530-2024 artfynd.xlsx
+++ b/artfynd/A 15530-2024 artfynd.xlsx
@@ -10336,7 +10336,7 @@
         <v>121329913</v>
       </c>
       <c r="B87" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>

--- a/artfynd/A 15530-2024 artfynd.xlsx
+++ b/artfynd/A 15530-2024 artfynd.xlsx
@@ -10336,7 +10336,7 @@
         <v>121329913</v>
       </c>
       <c r="B87" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>

--- a/artfynd/A 15530-2024 artfynd.xlsx
+++ b/artfynd/A 15530-2024 artfynd.xlsx
@@ -10336,7 +10336,7 @@
         <v>121329913</v>
       </c>
       <c r="B87" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>121405035</v>
       </c>
       <c r="B88" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 15530-2024 artfynd.xlsx
+++ b/artfynd/A 15530-2024 artfynd.xlsx
@@ -10336,7 +10336,7 @@
         <v>121329913</v>
       </c>
       <c r="B87" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>121405035</v>
       </c>
       <c r="B88" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 15530-2024 artfynd.xlsx
+++ b/artfynd/A 15530-2024 artfynd.xlsx
@@ -10336,7 +10336,7 @@
         <v>121329913</v>
       </c>
       <c r="B87" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>121405035</v>
       </c>
       <c r="B88" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 15530-2024 artfynd.xlsx
+++ b/artfynd/A 15530-2024 artfynd.xlsx
@@ -10336,7 +10336,7 @@
         <v>121329913</v>
       </c>
       <c r="B87" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>121405035</v>
       </c>
       <c r="B88" t="n">
-        <v>56568</v>
+        <v>56569</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>

--- a/artfynd/A 15530-2024 artfynd.xlsx
+++ b/artfynd/A 15530-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>33542656</v>
+        <v>116558734</v>
       </c>
       <c r="B2" t="n">
-        <v>56539</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Torpaskogsberget, Hakunge, Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685919.2110185511</v>
+        <v>685748</v>
       </c>
       <c r="R2" t="n">
-        <v>6605118.401817876</v>
+        <v>6605557</v>
       </c>
       <c r="S2" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-07-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-07-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 vuxna + 3 ungar</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,74 +760,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rudolf Edelberger</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rudolf Edelberger, Kari Ottesen</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>51021575</v>
+        <v>116548922</v>
       </c>
       <c r="B3" t="n">
-        <v>55803</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102952</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Torpaskogsberget, Hakunge, Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685919.2110185511</v>
+        <v>685720</v>
       </c>
       <c r="R3" t="n">
-        <v>6605118.401817876</v>
+        <v>6605075</v>
       </c>
       <c r="S3" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,27 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fortfarande kvar på Hakungeåkrarna</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,27 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans-Georg Wallentinus</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans-Georg Wallentinus</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113798453</v>
+        <v>116551085</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,35 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686030</v>
+        <v>685941</v>
       </c>
       <c r="R4" t="n">
-        <v>6605270</v>
+        <v>6605023</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:38</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,74 +962,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Fridström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Fridström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116548213</v>
+        <v>116556580</v>
       </c>
       <c r="B5" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Nybygget, Nybygget, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685660</v>
+        <v>685814</v>
       </c>
       <c r="R5" t="n">
-        <v>6605115</v>
+        <v>6605607</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,30 +1046,39 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1156,15 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116555386</v>
+        <v>116547239</v>
       </c>
       <c r="B6" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,34 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685969</v>
+        <v>685724</v>
       </c>
       <c r="R6" t="n">
-        <v>6605598</v>
+        <v>6605230</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116549358</v>
+        <v>116549295</v>
       </c>
       <c r="B7" t="n">
-        <v>90468</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685738</v>
+        <v>685747</v>
       </c>
       <c r="R7" t="n">
-        <v>6605019</v>
+        <v>6605048</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,15 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116549665</v>
+        <v>116550637</v>
       </c>
       <c r="B8" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,42 +1302,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685705</v>
+        <v>685912</v>
       </c>
       <c r="R8" t="n">
-        <v>6605069</v>
+        <v>6605009</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,19 +1359,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,12 +1376,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1489,53 +1392,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116551933</v>
+        <v>116551917</v>
       </c>
       <c r="B9" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685979</v>
+        <v>685968</v>
       </c>
       <c r="R9" t="n">
-        <v>6605103</v>
+        <v>6605055</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,9 +1474,24 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fjolårets, bestämt efter den vita mycelmattan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,12 +1506,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1595,62 +1522,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116557236</v>
+        <v>116548539</v>
       </c>
       <c r="B10" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nybygget (Nybygget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685775</v>
+        <v>685656</v>
       </c>
       <c r="R10" t="n">
-        <v>6605566</v>
+        <v>6605076</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,19 +1590,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,12 +1607,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1720,15 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116556168</v>
+        <v>116548029</v>
       </c>
       <c r="B11" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,37 +1634,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685866</v>
+        <v>685679</v>
       </c>
       <c r="R11" t="n">
-        <v>6605624</v>
+        <v>6605143</v>
       </c>
       <c r="S11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,9 +1691,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,12 +1718,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1826,50 +1734,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116548539</v>
+        <v>116549358</v>
       </c>
       <c r="B12" t="n">
-        <v>90851</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685656</v>
+        <v>685738</v>
       </c>
       <c r="R12" t="n">
-        <v>6605076</v>
+        <v>6605019</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,65 +1835,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116557128</v>
+        <v>116546753</v>
       </c>
       <c r="B13" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nybygget (Nybygget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685784</v>
+        <v>685780</v>
       </c>
       <c r="R13" t="n">
-        <v>6605588</v>
+        <v>6605374</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2017,40 +1903,29 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2061,55 +1936,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116559198</v>
+        <v>116547507</v>
       </c>
       <c r="B14" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nybygget (Nybygget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685752</v>
+        <v>685748</v>
       </c>
       <c r="R14" t="n">
-        <v>6605586</v>
+        <v>6605201</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2141,7 +2006,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2016,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,53 +2047,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116548410</v>
+        <v>116548728</v>
       </c>
       <c r="B15" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685667</v>
+        <v>685705</v>
       </c>
       <c r="R15" t="n">
-        <v>6605098</v>
+        <v>6605055</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2255,19 +2115,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,12 +2132,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2298,53 +2148,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116549389</v>
+        <v>116549166</v>
       </c>
       <c r="B16" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685731</v>
+        <v>685709</v>
       </c>
       <c r="R16" t="n">
-        <v>6605026</v>
+        <v>6605066</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2371,9 +2216,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,12 +2243,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2404,50 +2259,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116548446</v>
+        <v>116549651</v>
       </c>
       <c r="B17" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685659</v>
+        <v>685711</v>
       </c>
       <c r="R17" t="n">
-        <v>6605090</v>
+        <v>6605062</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,53 +2360,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116558639</v>
+        <v>116550376</v>
       </c>
       <c r="B18" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685748</v>
+        <v>685802</v>
       </c>
       <c r="R18" t="n">
-        <v>6605557</v>
+        <v>6605096</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2583,9 +2428,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,12 +2455,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2616,15 +2471,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116556335</v>
+        <v>116553715</v>
       </c>
       <c r="B19" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,42 +2482,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nybygget (Nybygget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685825</v>
+        <v>686015</v>
       </c>
       <c r="R19" t="n">
-        <v>6605652</v>
+        <v>6605440</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2694,19 +2539,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2721,12 +2556,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2737,15 +2572,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>116557978</v>
+        <v>116555255</v>
       </c>
       <c r="B20" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,37 +2583,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685772</v>
+        <v>686003</v>
       </c>
       <c r="R20" t="n">
-        <v>6605534</v>
+        <v>6605524</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2810,9 +2640,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,12 +2667,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2843,15 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>116547239</v>
+        <v>116555783</v>
       </c>
       <c r="B21" t="n">
-        <v>94549</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2859,37 +2694,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Nybygget, Nybygget, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685724</v>
+        <v>685941</v>
       </c>
       <c r="R21" t="n">
-        <v>6605230</v>
+        <v>6605662</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2916,9 +2751,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,12 +2778,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2949,53 +2794,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116546990</v>
+        <v>116556762</v>
       </c>
       <c r="B22" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685737</v>
+        <v>685814</v>
       </c>
       <c r="R22" t="n">
-        <v>6605252</v>
+        <v>6605597</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3022,19 +2862,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3049,12 +2879,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3065,50 +2895,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>116548728</v>
+        <v>113798453</v>
       </c>
       <c r="B23" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685705</v>
+        <v>686030</v>
       </c>
       <c r="R23" t="n">
-        <v>6605055</v>
+        <v>6605270</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3135,12 +2961,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3155,74 +2991,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Tomas Fridström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116551503</v>
+        <v>116546646</v>
       </c>
       <c r="B24" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>685933</v>
+        <v>685780</v>
       </c>
       <c r="R24" t="n">
-        <v>6605047</v>
+        <v>6605412</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3249,19 +3071,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3276,12 +3088,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3292,55 +3104,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>116546802</v>
+        <v>116546990</v>
       </c>
       <c r="B25" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>685786</v>
+        <v>685737</v>
       </c>
       <c r="R25" t="n">
-        <v>6605360</v>
+        <v>6605252</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3372,7 +3174,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3382,7 +3184,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3413,53 +3215,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116549295</v>
+        <v>116547913</v>
       </c>
       <c r="B26" t="n">
-        <v>91721</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>685747</v>
+        <v>685691</v>
       </c>
       <c r="R26" t="n">
-        <v>6605048</v>
+        <v>6605114</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3486,9 +3283,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3503,12 +3310,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3519,55 +3326,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116555310</v>
+        <v>116548023</v>
       </c>
       <c r="B27" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>685963</v>
+        <v>685676</v>
       </c>
       <c r="R27" t="n">
-        <v>6605570</v>
+        <v>6605109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3630,53 +3427,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116553601</v>
+        <v>116548410</v>
       </c>
       <c r="B28" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>685990</v>
+        <v>685667</v>
       </c>
       <c r="R28" t="n">
-        <v>6605400</v>
+        <v>6605098</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3703,9 +3495,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3720,12 +3522,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3736,15 +3538,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>116548453</v>
+        <v>116548446</v>
       </c>
       <c r="B29" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3752,42 +3549,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>685667</v>
+        <v>685659</v>
       </c>
       <c r="R29" t="n">
-        <v>6605098</v>
+        <v>6605090</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3814,19 +3606,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,12 +3623,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3857,15 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>116556461</v>
+        <v>116549389</v>
       </c>
       <c r="B30" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3893,14 +3670,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685836</v>
+        <v>685731</v>
       </c>
       <c r="R30" t="n">
-        <v>6605647</v>
+        <v>6605026</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3963,15 +3740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>116559276</v>
+        <v>116550538</v>
       </c>
       <c r="B31" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3979,37 +3751,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685751</v>
+        <v>685895</v>
       </c>
       <c r="R31" t="n">
-        <v>6605580</v>
+        <v>6605021</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4069,58 +3841,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>116555961</v>
+        <v>116550598</v>
       </c>
       <c r="B32" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nybygget (Nybygget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685928</v>
+        <v>685917</v>
       </c>
       <c r="R32" t="n">
-        <v>6605668</v>
+        <v>6605018</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4147,19 +3909,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4174,12 +3926,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4190,15 +3942,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>116546646</v>
+        <v>116550819</v>
       </c>
       <c r="B33" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4226,17 +3973,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>685780</v>
+        <v>685914</v>
       </c>
       <c r="R33" t="n">
-        <v>6605412</v>
+        <v>6605022</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4263,9 +4010,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4280,12 +4037,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4296,15 +4053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>116547913</v>
+        <v>116552637</v>
       </c>
       <c r="B34" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4332,14 +4084,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>685691</v>
+        <v>685914</v>
       </c>
       <c r="R34" t="n">
-        <v>6605114</v>
+        <v>6605139</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4371,7 +4123,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4381,7 +4133,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4412,58 +4164,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>116553686</v>
+        <v>116555209</v>
       </c>
       <c r="B35" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>685989</v>
+        <v>685991</v>
       </c>
       <c r="R35" t="n">
-        <v>6605427</v>
+        <v>6605507</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4490,19 +4232,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4517,12 +4249,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4533,15 +4265,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>116551085</v>
+        <v>116555766</v>
       </c>
       <c r="B36" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,34 +4276,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>685941</v>
+        <v>685924</v>
       </c>
       <c r="R36" t="n">
-        <v>6605023</v>
+        <v>6605688</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4639,53 +4366,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>116550376</v>
+        <v>116555862</v>
       </c>
       <c r="B37" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>685802</v>
+        <v>685930</v>
       </c>
       <c r="R37" t="n">
-        <v>6605096</v>
+        <v>6605673</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4712,19 +4434,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4739,12 +4451,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4755,53 +4467,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>116558797</v>
+        <v>116556168</v>
       </c>
       <c r="B38" t="n">
-        <v>4769</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>685737</v>
+        <v>685866</v>
       </c>
       <c r="R38" t="n">
-        <v>6605557</v>
+        <v>6605624</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4861,64 +4568,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>116556581</v>
+        <v>116556236</v>
       </c>
       <c r="B39" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685828</v>
+        <v>685854</v>
       </c>
       <c r="R39" t="n">
-        <v>6605609</v>
+        <v>6605631</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4981,58 +4669,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>116549263</v>
+        <v>116556318</v>
       </c>
       <c r="B40" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>685713</v>
+        <v>685841</v>
       </c>
       <c r="R40" t="n">
-        <v>6605066</v>
+        <v>6605639</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5059,19 +4737,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5086,12 +4754,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5102,59 +4770,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>116549736</v>
+        <v>116556461</v>
       </c>
       <c r="B41" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685721</v>
+        <v>685836</v>
       </c>
       <c r="R41" t="n">
-        <v>6605078</v>
+        <v>6605647</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5195,7 +4849,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5218,64 +4871,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>116557148</v>
+        <v>116558451</v>
       </c>
       <c r="B42" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685793</v>
+        <v>685757</v>
       </c>
       <c r="R42" t="n">
-        <v>6605578</v>
+        <v>6605550</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5338,15 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>116550538</v>
+        <v>116558639</v>
       </c>
       <c r="B43" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5374,14 +5003,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685895</v>
+        <v>685748</v>
       </c>
       <c r="R43" t="n">
-        <v>6605021</v>
+        <v>6605557</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5444,15 +5073,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>116553715</v>
+        <v>116548453</v>
       </c>
       <c r="B44" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5460,37 +5084,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>686015</v>
+        <v>685667</v>
       </c>
       <c r="R44" t="n">
-        <v>6605440</v>
+        <v>6605098</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5517,9 +5146,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5534,12 +5173,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5550,15 +5189,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>116557805</v>
+        <v>116548611</v>
       </c>
       <c r="B45" t="n">
-        <v>4769</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5566,34 +5200,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>685769</v>
+        <v>685682</v>
       </c>
       <c r="R45" t="n">
-        <v>6605547</v>
+        <v>6605058</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5656,15 +5295,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>116550408</v>
+        <v>116549665</v>
       </c>
       <c r="B46" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5672,39 +5306,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>685806</v>
+        <v>685705</v>
       </c>
       <c r="R46" t="n">
-        <v>6605097</v>
+        <v>6605069</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5736,7 +5370,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5746,7 +5380,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5777,15 +5411,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>116556762</v>
+        <v>116559198</v>
       </c>
       <c r="B47" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5793,37 +5422,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Nybygget, Nybygget, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685814</v>
+        <v>685752</v>
       </c>
       <c r="R47" t="n">
-        <v>6605597</v>
+        <v>6605586</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5850,9 +5484,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5867,12 +5511,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5883,53 +5527,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>116555862</v>
+        <v>116559276</v>
       </c>
       <c r="B48" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>685930</v>
+        <v>685751</v>
       </c>
       <c r="R48" t="n">
-        <v>6605673</v>
+        <v>6605580</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5989,37 +5628,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>116556738</v>
+        <v>40102002</v>
       </c>
       <c r="B49" t="n">
-        <v>104860</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57838</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>100100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6027,29 +5661,24 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Hakunge, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>685810</v>
+        <v>685919</v>
       </c>
       <c r="R49" t="n">
-        <v>6605599</v>
+        <v>6605118</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6073,12 +5702,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2011-08-12</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2011-08-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Låg och snurrade över skogskanten ett tag. Även ett ex. 11/8 på samma ställe.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6093,69 +5737,74 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Hans-Georg Wallentinus</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Hans-Georg Wallentinus</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>116550819</v>
+        <v>37518437</v>
       </c>
       <c r="B50" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Hakunge, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>685914</v>
+        <v>685919</v>
       </c>
       <c r="R50" t="n">
-        <v>6605022</v>
+        <v>6605118</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6179,22 +5828,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2010-12-29</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2010-12-29</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>flög upp från vägen, många spår och spillning i närheten</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6209,31 +5863,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Rudolf Edelberger</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Rudolf Edelberger, Kari Ottesen</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>116550637</v>
+        <v>116546689</v>
       </c>
       <c r="B51" t="n">
-        <v>91721</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6241,34 +5886,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>685912</v>
+        <v>685782</v>
       </c>
       <c r="R51" t="n">
-        <v>6605009</v>
+        <v>6605394</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6331,15 +5988,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>116546689</v>
+        <v>116549427</v>
       </c>
       <c r="B52" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6364,29 +6016,22 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>685782</v>
+        <v>685735</v>
       </c>
       <c r="R52" t="n">
-        <v>6605394</v>
+        <v>6605018</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6449,50 +6094,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>116548029</v>
+        <v>116551048</v>
       </c>
       <c r="B53" t="n">
-        <v>90468</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Hakunge, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>685679</v>
+        <v>685950</v>
       </c>
       <c r="R53" t="n">
-        <v>6605143</v>
+        <v>6605013</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6522,19 +6167,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:43</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:43</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6549,12 +6184,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6565,15 +6200,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>116555384</v>
+        <v>116555310</v>
       </c>
       <c r="B54" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6581,42 +6211,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Nybygget (Nybygget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>685973</v>
+        <v>685963</v>
       </c>
       <c r="R54" t="n">
-        <v>6605545</v>
+        <v>6605570</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6643,19 +6273,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6670,12 +6290,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6686,53 +6306,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>116550598</v>
+        <v>116555961</v>
       </c>
       <c r="B55" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Nybygget, Nybygget, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>685917</v>
+        <v>685928</v>
       </c>
       <c r="R55" t="n">
-        <v>6605018</v>
+        <v>6605668</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6759,9 +6379,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6776,12 +6406,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6792,50 +6422,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>116556318</v>
+        <v>116546759</v>
       </c>
       <c r="B56" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685841</v>
+        <v>685780</v>
       </c>
       <c r="R56" t="n">
-        <v>6605639</v>
+        <v>6605373</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6876,6 +6510,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6898,15 +6533,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>116546972</v>
+        <v>116546802</v>
       </c>
       <c r="B57" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6932,28 +6562,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685741</v>
+        <v>685786</v>
       </c>
       <c r="R57" t="n">
-        <v>6605232</v>
+        <v>6605360</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6980,30 +6606,39 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -7014,15 +6649,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>116549427</v>
+        <v>116546972</v>
       </c>
       <c r="B58" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7030,39 +6660,43 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685735</v>
+        <v>685741</v>
       </c>
       <c r="R58" t="n">
-        <v>6605018</v>
+        <v>6605232</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7103,6 +6737,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7125,58 +6760,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>116548611</v>
+        <v>116549263</v>
       </c>
       <c r="B59" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685682</v>
+        <v>685713</v>
       </c>
       <c r="R59" t="n">
-        <v>6605058</v>
+        <v>6605066</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7203,9 +6833,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7220,12 +6860,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7236,50 +6876,54 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>116548922</v>
+        <v>116549736</v>
       </c>
       <c r="B60" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685720</v>
+        <v>685721</v>
       </c>
       <c r="R60" t="n">
-        <v>6605075</v>
+        <v>6605078</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7320,6 +6964,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7342,15 +6987,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>116555255</v>
+        <v>116551148</v>
       </c>
       <c r="B61" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7358,37 +6998,46 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>686003</v>
+        <v>685941</v>
       </c>
       <c r="R61" t="n">
-        <v>6605524</v>
+        <v>6605023</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7415,39 +7064,30 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7458,15 +7098,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>116549297</v>
+        <v>27855674</v>
       </c>
       <c r="B62" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7474,42 +7109,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>102118</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Hakunge, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685713</v>
+        <v>685919</v>
       </c>
       <c r="R62" t="n">
-        <v>6605063</v>
+        <v>6605118</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7533,22 +7172,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2007-06-03</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2007-06-03</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7563,31 +7202,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Stockholms rapportkommitté</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Hans-Erik Nordin, Hans-Georg Wallentinus</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>116546753</v>
+        <v>116557805</v>
       </c>
       <c r="B63" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7595,34 +7225,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685780</v>
+        <v>685769</v>
       </c>
       <c r="R63" t="n">
-        <v>6605374</v>
+        <v>6605547</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7685,15 +7315,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>116555922</v>
+        <v>116558797</v>
       </c>
       <c r="B64" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7701,42 +7326,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>102306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nybygget (Nybygget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685934</v>
+        <v>685737</v>
       </c>
       <c r="R64" t="n">
-        <v>6605666</v>
+        <v>6605557</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7763,19 +7383,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7790,12 +7400,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7806,69 +7416,57 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>116551193</v>
+        <v>29765441</v>
       </c>
       <c r="B65" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Hakunge, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685968</v>
+        <v>685919</v>
       </c>
       <c r="R65" t="n">
-        <v>6605041</v>
+        <v>6605118</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7892,12 +7490,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2008-06-07</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2008-06-07</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Kan ha varit två</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7906,76 +7519,85 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Hans-Georg Wallentinus</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Hans-Georg Wallentinus</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>116556236</v>
+        <v>39143585</v>
       </c>
       <c r="B66" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>102623</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Hakunge, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685854</v>
+        <v>685919</v>
       </c>
       <c r="R66" t="n">
-        <v>6605631</v>
+        <v>6605118</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7999,12 +7621,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2011-05-21</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2011-05-21</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Andra M efter Marieberg. Inga nattskärror än.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8019,69 +7656,69 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Björn Wallentinus</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Björn Wallentinus, Hans-Georg Wallentinus</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>116552637</v>
+        <v>51021575</v>
       </c>
       <c r="B67" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>102952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Hakunge, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>685914</v>
+        <v>685919</v>
       </c>
       <c r="R67" t="n">
-        <v>6605139</v>
+        <v>6605118</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8105,22 +7742,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Fortfarande kvar på Hakungeåkrarna</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8135,69 +7777,69 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Hans-Georg Wallentinus</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Hans-Georg Wallentinus</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>116549651</v>
+        <v>33542656</v>
       </c>
       <c r="B68" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Hakunge, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>685711</v>
+        <v>685919</v>
       </c>
       <c r="R68" t="n">
-        <v>6605062</v>
+        <v>6605118</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8221,12 +7863,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2009-07-26</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2009-07-26</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2 vuxna + 3 ungar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8241,31 +7898,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Rudolf Edelberger</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Rudolf Edelberger, Kari Ottesen</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>116547507</v>
+        <v>116547434</v>
       </c>
       <c r="B69" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8273,34 +7921,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>685748</v>
+        <v>685747</v>
       </c>
       <c r="R69" t="n">
-        <v>6605201</v>
+        <v>6605205</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8332,7 +7985,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8342,7 +7995,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8373,15 +8026,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>116551917</v>
+        <v>116549297</v>
       </c>
       <c r="B70" t="n">
-        <v>91721</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8389,48 +8037,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>685968</v>
+        <v>685713</v>
       </c>
       <c r="R70" t="n">
-        <v>6605055</v>
+        <v>6605063</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8462,7 +8101,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8472,12 +8111,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Fjolårets, bestämt efter den vita mycelmattan.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8508,50 +8142,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>116555209</v>
+        <v>116549746</v>
       </c>
       <c r="B71" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>685991</v>
+        <v>685721</v>
       </c>
       <c r="R71" t="n">
-        <v>6605507</v>
+        <v>6605078</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8592,6 +8230,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8614,15 +8253,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>116551048</v>
+        <v>116555384</v>
       </c>
       <c r="B72" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8630,42 +8264,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Hakunge), Upl</t>
+          <t>Nybygget, Nybygget, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>685950</v>
+        <v>685973</v>
       </c>
       <c r="R72" t="n">
-        <v>6605013</v>
+        <v>6605545</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8692,9 +8326,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8709,12 +8353,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8725,15 +8369,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>116551148</v>
+        <v>116557978</v>
       </c>
       <c r="B73" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8741,43 +8380,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>685941</v>
+        <v>685772</v>
       </c>
       <c r="R73" t="n">
-        <v>6605023</v>
+        <v>6605534</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8818,7 +8448,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8841,53 +8470,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>116558451</v>
+        <v>116559226</v>
       </c>
       <c r="B74" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Nybygget, Nybygget, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>685757</v>
+        <v>685749</v>
       </c>
       <c r="R74" t="n">
-        <v>6605550</v>
+        <v>6605588</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8914,9 +8543,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8931,12 +8570,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8947,15 +8586,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>116559226</v>
+        <v>116553138</v>
       </c>
       <c r="B75" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8963,39 +8597,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Nybygget (Nybygget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>685749</v>
+        <v>685975</v>
       </c>
       <c r="R75" t="n">
-        <v>6605588</v>
+        <v>6605249</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -9027,7 +8661,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9037,7 +8671,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9068,15 +8702,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>116549746</v>
+        <v>116553601</v>
       </c>
       <c r="B76" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9084,43 +8713,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>685721</v>
+        <v>685990</v>
       </c>
       <c r="R76" t="n">
-        <v>6605078</v>
+        <v>6605400</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9161,7 +8781,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9184,53 +8803,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>116556580</v>
+        <v>116555386</v>
       </c>
       <c r="B77" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Nybygget (Nybygget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>685814</v>
+        <v>685969</v>
       </c>
       <c r="R77" t="n">
-        <v>6605607</v>
+        <v>6605598</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9257,19 +8871,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9284,12 +8888,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9300,53 +8904,53 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>116558734</v>
+        <v>116555922</v>
       </c>
       <c r="B78" t="n">
-        <v>78085</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Nybygget, Nybygget, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685748</v>
+        <v>685934</v>
       </c>
       <c r="R78" t="n">
-        <v>6605557</v>
+        <v>6605666</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9373,9 +8977,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9390,12 +9004,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9406,15 +9020,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>116549166</v>
+        <v>116556335</v>
       </c>
       <c r="B79" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9422,34 +9031,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Nybygget, Nybygget, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>685709</v>
+        <v>685825</v>
       </c>
       <c r="R79" t="n">
-        <v>6605066</v>
+        <v>6605652</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9481,7 +9095,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9491,7 +9105,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9522,15 +9136,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>116547434</v>
+        <v>116548213</v>
       </c>
       <c r="B80" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9538,42 +9147,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685747</v>
+        <v>685660</v>
       </c>
       <c r="R80" t="n">
-        <v>6605205</v>
+        <v>6605115</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9600,39 +9213,30 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9643,15 +9247,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>116555783</v>
+        <v>116550408</v>
       </c>
       <c r="B81" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9659,34 +9258,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Nybygget (Nybygget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>685941</v>
+        <v>685806</v>
       </c>
       <c r="R81" t="n">
-        <v>6605662</v>
+        <v>6605097</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9718,7 +9322,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9728,7 +9332,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9759,15 +9363,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>116558094</v>
+        <v>116551503</v>
       </c>
       <c r="B82" t="n">
-        <v>56244</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9775,37 +9374,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>208255</v>
+        <v>106554</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>685768</v>
+        <v>685933</v>
       </c>
       <c r="R82" t="n">
-        <v>6605543</v>
+        <v>6605047</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9832,9 +9436,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9849,12 +9463,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9865,62 +9479,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>116557996</v>
+        <v>116551933</v>
       </c>
       <c r="B83" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Nybygget (Nybygget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685765</v>
+        <v>685979</v>
       </c>
       <c r="R83" t="n">
-        <v>6605584</v>
+        <v>6605103</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9947,19 +9547,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9974,12 +9564,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9990,53 +9580,53 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>116548023</v>
+        <v>116553686</v>
       </c>
       <c r="B84" t="n">
-        <v>79058</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>106554</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685676</v>
+        <v>685989</v>
       </c>
       <c r="R84" t="n">
-        <v>6605109</v>
+        <v>6605427</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10063,9 +9653,19 @@
           <t>2024-05-04</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10080,12 +9680,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -10096,15 +9696,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>116553138</v>
+        <v>116558094</v>
       </c>
       <c r="B85" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10112,42 +9707,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>208255</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>685975</v>
+        <v>685768</v>
       </c>
       <c r="R85" t="n">
-        <v>6605249</v>
+        <v>6605543</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10174,19 +9764,9 @@
           <t>2024-05-04</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10201,12 +9781,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10217,15 +9797,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>116546759</v>
+        <v>116552748</v>
       </c>
       <c r="B86" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10233,43 +9808,48 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100526</v>
+        <v>219790</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Torpaskogsberget (Torpaskogsberget), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685780</v>
+        <v>685905</v>
       </c>
       <c r="R86" t="n">
-        <v>6605373</v>
+        <v>6605162</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10310,7 +9890,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10333,15 +9912,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121329913</v>
+        <v>116551193</v>
       </c>
       <c r="B87" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10368,7 +9942,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>147</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10376,22 +9950,26 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Torpaskogsberget  (*knärot* /stjälk/), Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>685799</v>
+        <v>685968</v>
       </c>
       <c r="R87" t="n">
-        <v>6605587</v>
+        <v>6605041</v>
       </c>
       <c r="S87" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10411,11 +9989,6 @@
       <c r="W87" t="inlineStr">
         <is>
           <t>Össeby-Garn</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>AB-Val-0116</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -10441,81 +10014,76 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Permats</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Nya Tärnan gruppen</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121405035</v>
+        <v>116552174</v>
       </c>
       <c r="B88" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Torpaskogsberget, Hakunge, Upl</t>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>685919</v>
+        <v>686001</v>
       </c>
       <c r="R88" t="n">
-        <v>6605118</v>
+        <v>6605084</v>
       </c>
       <c r="S88" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10539,22 +10107,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10563,21 +10131,854 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Michael Staff</t>
+          <t>Martin Permats</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michael Staff</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>116556581</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>685828</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6605609</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>116557128</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Nybygget, Nybygget, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>685784</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6605588</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>116557148</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>685793</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6605578</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>116557236</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Nybygget, Nybygget, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>685775</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6605566</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>116557996</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Nybygget, Nybygget, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>685765</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6605584</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>121329913</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Torpaskogsberget  (*knärot* /stjälk/), Upl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>685799</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6605587</v>
+      </c>
+      <c r="S94" t="n">
+        <v>62</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>AB-Val-0116</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>116556738</v>
+      </c>
+      <c r="B95" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Torpaskogsberget, Torpaskogsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>685810</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6605599</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
